--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportInventorySemiProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportInventorySemiProductTemplate.xlsx
@@ -21,12 +21,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>Tên sản phẩm</t>
-  </si>
-  <si>
-    <t>Lô nguyên liệu</t>
-  </si>
-  <si>
     <t>SET</t>
   </si>
   <si>
@@ -49,6 +43,12 @@
   </si>
   <si>
     <t>Block/SH</t>
+  </si>
+  <si>
+    <t>Tên sản phẩm KC</t>
+  </si>
+  <si>
+    <t>Số lô tấm nguyên liệu</t>
   </si>
 </sst>
 </file>
@@ -420,34 +420,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportInventorySemiProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportInventorySemiProductTemplate.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,6 +121,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -408,7 +411,7 @@
   <cols>
     <col min="1" max="2" width="25" style="3" customWidth="1"/>
     <col min="3" max="3" width="24" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="4" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" style="3" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" style="3" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" style="3" customWidth="1"/>
@@ -428,7 +431,7 @@
       <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
